--- a/influencer_forms/029_podcast_guest_form--influencer_forms.xlsx
+++ b/influencer_forms/029_podcast_guest_form--influencer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -921,167 +921,6 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Output File</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Output File</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>influencer_forms</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Influencer Forms</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1148,590 +987,182 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>comedy</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Comedy</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gaming</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>description_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>this_is_an_example_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>This is an example form</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>description_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>this_is_an_example_description</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>This is an example description</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>influencer_forms</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Influencer Forms</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>music</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Music</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>art</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Art</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>comedy</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Comedy</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sports</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>gaming</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>description_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>collect_and_manage_podcast_guest_applications_online_with_our_free_podcast_guest_form._add_your_logo_and_a_file_upload_field._customize_and_embed_in_seconds!</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Collect and manage podcast guest applications online with our free Podcast Guest Form. Add your logo and a file upload field. Customize and embed in seconds!</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>description_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customize_and_manage_podcast_guest_applications_online_with_our_free_podcast_guest_form._add_your_logo_and_a_file_upload_field.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Customize and manage podcast guest applications online with our free Podcast Guest Form. Add your logo and a file upload field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>influencer_forms</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Influencer Forms</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>music</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Music</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>art</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Art</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comedy</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comedy</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sports</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>gaming</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>description_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>this_is_an_example_form.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>This is an example form.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>description_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>this_is_an_example_description.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>This is an example description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>podcast_guest_form</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Podcast Guest Form</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>other</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
